--- a/ValueSet-stroke-risk-factor-vs.xlsx
+++ b/ValueSet-stroke-risk-factor-vs.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07</t>
+    <t>2026-10-27</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,19 +86,19 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Defines the SNOMED CT codes for conditions or risk factors relevant to stroke, including an option for unknown status.</t>
+    <t>Defines standard and locally governed conditions or assertions relevant to stroke risk, including an option for unknown status.</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>To aggregate core stroke risk factors and unknown/absent problem concepts for comprehensive capture and validation.</t>
+    <t>To aggregate core stroke risk factors, locally governed RES-Q assertions, and unknown/absent problem concepts for comprehensive capture and validation.</t>
   </si>
   <si>
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes SNOMED CT® content and may include HL7 IPS value set content. SNOMED CT® is distributed by SNOMED International.</t>
+    <t>This value set includes SNOMED CT® content, locally governed RES-Q concepts, and may include HL7 IPS value set content. SNOMED CT® is distributed by SNOMED International.</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -110,6 +111,18 @@
   </si>
   <si>
     <t>http://testSK.org/ValueSet/stroke-risk-factor-snomed-vs</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://qualityregistry.org/CodeSystem/stroke-risk-factor-cs</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/uv/ips/ValueSet/absent-or-unknown-problems-uv-ips</t>
@@ -404,6 +417,46 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -418,7 +471,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
